--- a/think3d_repro/outputs/run2/vlmeval_runs/SPAgent_4B_no_tools_general/VSIBench/SPAgent_4B_no_tools_general_VSIBench.xlsx
+++ b/think3d_repro/outputs/run2/vlmeval_runs/SPAgent_4B_no_tools_general/VSIBench/SPAgent_4B_no_tools_general_VSIBench.xlsx
@@ -5970,7 +5970,7 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>6.770458221435547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5999,7 +5999,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>30.21363854408264</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -6028,7 +6028,7 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>4.364361047744751</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -6057,7 +6057,7 @@
         <v>1</v>
       </c>
       <c r="I5">
-        <v>42.46664905548096</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -6086,7 +6086,7 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>4.055455923080444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -6115,7 +6115,7 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>3.808656454086304</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -6144,7 +6144,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>5.425893545150757</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -6173,7 +6173,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>3.498968124389648</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -6202,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>3.026595115661621</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -6231,7 +6231,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>7.579338312149048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -6260,7 +6260,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>5.992135524749756</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -6289,7 +6289,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>4.654220581054688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -6318,7 +6318,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>4.470521926879883</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -6347,7 +6347,7 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>10.14037132263184</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -6376,7 +6376,7 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>3.460659980773926</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -6405,7 +6405,7 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>4.702566862106323</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -6434,7 +6434,7 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>4.021833896636963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -6463,7 +6463,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>5.4377281665802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -6492,7 +6492,7 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>3.751674890518188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -6521,7 +6521,7 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>3.952949523925781</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -6550,7 +6550,7 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>4.457127332687378</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>9.407248497009277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -6608,7 +6608,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>19.27677822113037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -6637,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>35.06149864196777</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>2.977995634078979</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -6695,7 +6695,7 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>4.649582862854004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -6724,7 +6724,7 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>12.97561240196228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -6753,7 +6753,7 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>3.588784217834473</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -6782,7 +6782,7 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>9.079164505004883</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -6811,7 +6811,7 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>5.367563247680664</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -6840,7 +6840,7 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>4.180601119995117</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -6869,7 +6869,7 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>3.74259352684021</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -6898,7 +6898,7 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>6.576267719268799</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -6927,7 +6927,7 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>4.038628816604614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -6956,7 +6956,7 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>4.932912349700928</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -6985,7 +6985,7 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>7.753219604492188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -7014,7 +7014,7 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>2.531129837036133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>3.446134805679321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -7072,7 +7072,7 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>3.898154735565186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -7101,7 +7101,7 @@
         <v>1</v>
       </c>
       <c r="I41">
-        <v>3.414251804351807</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -7130,7 +7130,7 @@
         <v>1</v>
       </c>
       <c r="I42">
-        <v>5.059915065765381</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -7159,7 +7159,7 @@
         <v>1</v>
       </c>
       <c r="I43">
-        <v>10.92520809173584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -7188,7 +7188,7 @@
         <v>0</v>
       </c>
       <c r="I44">
-        <v>7.29842472076416</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -7217,7 +7217,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>5.408496618270874</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -7246,7 +7246,7 @@
         <v>1</v>
       </c>
       <c r="I46">
-        <v>5.179645299911499</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -7275,7 +7275,7 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>5.432847738265991</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="I48">
-        <v>7.598723649978638</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -7333,7 +7333,7 @@
         <v>0</v>
       </c>
       <c r="I49">
-        <v>3.565226793289185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -7362,7 +7362,7 @@
         <v>0</v>
       </c>
       <c r="I50">
-        <v>8.728394508361816</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -7391,7 +7391,7 @@
         <v>1</v>
       </c>
       <c r="I51">
-        <v>2.390063047409058</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -7420,7 +7420,7 @@
         <v>0</v>
       </c>
       <c r="I52">
-        <v>5.023765325546265</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -7449,7 +7449,7 @@
         <v>1</v>
       </c>
       <c r="I53">
-        <v>6.997445106506348</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -7478,7 +7478,7 @@
         <v>0</v>
       </c>
       <c r="I54">
-        <v>15.16775679588318</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -7507,7 +7507,7 @@
         <v>1</v>
       </c>
       <c r="I55">
-        <v>3.904839515686035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -7536,7 +7536,7 @@
         <v>1</v>
       </c>
       <c r="I56">
-        <v>10.15381264686584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -7565,7 +7565,7 @@
         <v>0</v>
       </c>
       <c r="I57">
-        <v>4.999703884124756</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -7594,7 +7594,7 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>8.498801946640015</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -7623,7 +7623,7 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>4.847135066986084</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -7652,7 +7652,7 @@
         <v>1</v>
       </c>
       <c r="I60">
-        <v>4.519110441207886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -7681,7 +7681,7 @@
         <v>0</v>
       </c>
       <c r="I61">
-        <v>5.792629241943359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -7710,7 +7710,7 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>7.457745790481567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -7739,7 +7739,7 @@
         <v>1</v>
       </c>
       <c r="I63">
-        <v>5.471017837524414</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -7768,7 +7768,7 @@
         <v>1</v>
       </c>
       <c r="I64">
-        <v>4.735137224197388</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -7797,7 +7797,7 @@
         <v>1</v>
       </c>
       <c r="I65">
-        <v>16.1621208190918</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -7826,7 +7826,7 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>7.380346059799194</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -7855,7 +7855,7 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>9.566175937652588</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -7884,7 +7884,7 @@
         <v>0</v>
       </c>
       <c r="I68">
-        <v>4.895838975906372</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -7913,7 +7913,7 @@
         <v>1</v>
       </c>
       <c r="I69">
-        <v>3.847241163253784</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -7942,7 +7942,7 @@
         <v>0</v>
       </c>
       <c r="I70">
-        <v>10.04754424095154</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -7971,7 +7971,7 @@
         <v>1</v>
       </c>
       <c r="I71">
-        <v>9.183750152587891</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -8000,7 +8000,7 @@
         <v>0</v>
       </c>
       <c r="I72">
-        <v>4.428146362304688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -8029,7 +8029,7 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>7.203106880187988</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -8058,7 +8058,7 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>4.829328775405884</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -8087,7 +8087,7 @@
         <v>0</v>
       </c>
       <c r="I75">
-        <v>4.325331926345825</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -8116,7 +8116,7 @@
         <v>0</v>
       </c>
       <c r="I76">
-        <v>5.201633930206299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -8145,7 +8145,7 @@
         <v>1</v>
       </c>
       <c r="I77">
-        <v>5.679288148880005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -8174,7 +8174,7 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>6.837411165237427</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -8203,7 +8203,7 @@
         <v>1</v>
       </c>
       <c r="I79">
-        <v>5.189610719680786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -8232,7 +8232,7 @@
         <v>0</v>
       </c>
       <c r="I80">
-        <v>5.706433296203613</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -8261,7 +8261,7 @@
         <v>0</v>
       </c>
       <c r="I81">
-        <v>4.793017864227295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -8290,7 +8290,7 @@
         <v>0</v>
       </c>
       <c r="I82">
-        <v>6.31278395652771</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -8319,7 +8319,7 @@
         <v>1</v>
       </c>
       <c r="I83">
-        <v>3.937890768051147</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -8348,7 +8348,7 @@
         <v>1</v>
       </c>
       <c r="I84">
-        <v>5.534330606460571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -8377,7 +8377,7 @@
         <v>0</v>
       </c>
       <c r="I85">
-        <v>10.02803540229797</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -8406,7 +8406,7 @@
         <v>0</v>
       </c>
       <c r="I86">
-        <v>6.279954433441162</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -8435,7 +8435,7 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>4.928526878356934</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -8464,7 +8464,7 @@
         <v>1</v>
       </c>
       <c r="I88">
-        <v>9.752679109573364</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -8493,7 +8493,7 @@
         <v>1</v>
       </c>
       <c r="I89">
-        <v>4.041256904602051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -8522,7 +8522,7 @@
         <v>0</v>
       </c>
       <c r="I90">
-        <v>6.054503679275513</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -8551,7 +8551,7 @@
         <v>0</v>
       </c>
       <c r="I91">
-        <v>6.890289545059204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -8580,7 +8580,7 @@
         <v>1</v>
       </c>
       <c r="I92">
-        <v>4.726924180984497</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -8609,7 +8609,7 @@
         <v>1</v>
       </c>
       <c r="I93">
-        <v>3.983577728271484</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -8638,7 +8638,7 @@
         <v>0</v>
       </c>
       <c r="I94">
-        <v>12.00625157356262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -8667,7 +8667,7 @@
         <v>0</v>
       </c>
       <c r="I95">
-        <v>8.103243589401245</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="I96">
-        <v>5.531793594360352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -8725,7 +8725,7 @@
         <v>0</v>
       </c>
       <c r="I97">
-        <v>12.41113066673279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -8754,7 +8754,7 @@
         <v>1</v>
       </c>
       <c r="I98">
-        <v>5.806511640548706</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -8783,7 +8783,7 @@
         <v>0</v>
       </c>
       <c r="I99">
-        <v>8.07194995880127</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -8812,7 +8812,7 @@
         <v>0</v>
       </c>
       <c r="I100">
-        <v>8.416966199874878</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -8841,7 +8841,7 @@
         <v>0</v>
       </c>
       <c r="I101">
-        <v>11.25810265541077</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -8870,7 +8870,7 @@
         <v>1</v>
       </c>
       <c r="I102">
-        <v>4.151492834091187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -8899,7 +8899,7 @@
         <v>0</v>
       </c>
       <c r="I103">
-        <v>5.155770063400269</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -8928,7 +8928,7 @@
         <v>0</v>
       </c>
       <c r="I104">
-        <v>8.323022127151489</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -8957,7 +8957,7 @@
         <v>1</v>
       </c>
       <c r="I105">
-        <v>4.3272545337677</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -8986,7 +8986,7 @@
         <v>1</v>
       </c>
       <c r="I106">
-        <v>6.237447500228882</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -9015,7 +9015,7 @@
         <v>0</v>
       </c>
       <c r="I107">
-        <v>7.368756771087646</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -9044,7 +9044,7 @@
         <v>1</v>
       </c>
       <c r="I108">
-        <v>6.649991512298584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -9073,7 +9073,7 @@
         <v>1</v>
       </c>
       <c r="I109">
-        <v>10.92091727256775</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -9102,7 +9102,7 @@
         <v>1</v>
       </c>
       <c r="I110">
-        <v>5.481883525848389</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -9131,7 +9131,7 @@
         <v>1</v>
       </c>
       <c r="I111">
-        <v>6.325336456298828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -9160,7 +9160,7 @@
         <v>1</v>
       </c>
       <c r="I112">
-        <v>5.223364591598511</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -9189,7 +9189,7 @@
         <v>1</v>
       </c>
       <c r="I113">
-        <v>5.818026304244995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -9218,7 +9218,7 @@
         <v>0</v>
       </c>
       <c r="I114">
-        <v>11.01411652565002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -9247,7 +9247,7 @@
         <v>0</v>
       </c>
       <c r="I115">
-        <v>5.281318187713623</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -9276,7 +9276,7 @@
         <v>0</v>
       </c>
       <c r="I116">
-        <v>12.20877647399902</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -9305,7 +9305,7 @@
         <v>1</v>
       </c>
       <c r="I117">
-        <v>8.999538898468018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -9334,7 +9334,7 @@
         <v>1</v>
       </c>
       <c r="I118">
-        <v>5.891892671585083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -9363,7 +9363,7 @@
         <v>1</v>
       </c>
       <c r="I119">
-        <v>5.188196420669556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -9392,7 +9392,7 @@
         <v>0</v>
       </c>
       <c r="I120">
-        <v>11.09502577781677</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -9421,7 +9421,7 @@
         <v>0</v>
       </c>
       <c r="I121">
-        <v>18.55655360221863</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -9450,7 +9450,7 @@
         <v>0</v>
       </c>
       <c r="I122">
-        <v>5.236891984939575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -9479,7 +9479,7 @@
         <v>1</v>
       </c>
       <c r="I123">
-        <v>9.52698802947998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -9508,7 +9508,7 @@
         <v>0</v>
       </c>
       <c r="I124">
-        <v>3.808156490325928</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -9537,7 +9537,7 @@
         <v>0</v>
       </c>
       <c r="I125">
-        <v>12.07310009002686</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -9566,7 +9566,7 @@
         <v>1</v>
       </c>
       <c r="I126">
-        <v>5.27874493598938</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -9595,7 +9595,7 @@
         <v>0</v>
       </c>
       <c r="I127">
-        <v>9.12078857421875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -9621,7 +9621,7 @@
         <v>0</v>
       </c>
       <c r="I128">
-        <v>4.604688405990601</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -9650,7 +9650,7 @@
         <v>0</v>
       </c>
       <c r="I129">
-        <v>8.27281665802002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -9679,7 +9679,7 @@
         <v>0</v>
       </c>
       <c r="I130">
-        <v>6.637580394744873</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="I131">
-        <v>10.13237166404724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -9737,7 +9737,7 @@
         <v>0</v>
       </c>
       <c r="I132">
-        <v>7.708694458007812</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -9766,7 +9766,7 @@
         <v>0</v>
       </c>
       <c r="I133">
-        <v>6.094782829284668</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -9795,7 +9795,7 @@
         <v>0</v>
       </c>
       <c r="I134">
-        <v>10.36117482185364</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -9824,7 +9824,7 @@
         <v>1</v>
       </c>
       <c r="I135">
-        <v>7.986688613891602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -9853,7 +9853,7 @@
         <v>0</v>
       </c>
       <c r="I136">
-        <v>5.197154521942139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -9882,7 +9882,7 @@
         <v>1</v>
       </c>
       <c r="I137">
-        <v>5.780331373214722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -9911,7 +9911,7 @@
         <v>0</v>
       </c>
       <c r="I138">
-        <v>6.483951330184937</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -9940,7 +9940,7 @@
         <v>0</v>
       </c>
       <c r="I139">
-        <v>5.027415752410889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -9969,7 +9969,7 @@
         <v>1</v>
       </c>
       <c r="I140">
-        <v>9.89415431022644</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -9998,7 +9998,7 @@
         <v>1</v>
       </c>
       <c r="I141">
-        <v>4.396966934204102</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -10027,7 +10027,7 @@
         <v>0</v>
       </c>
       <c r="I142">
-        <v>3.397907495498657</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -10056,7 +10056,7 @@
         <v>1</v>
       </c>
       <c r="I143">
-        <v>5.900333404541016</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -10085,7 +10085,7 @@
         <v>1</v>
       </c>
       <c r="I144">
-        <v>6.222262859344482</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -10114,7 +10114,7 @@
         <v>1</v>
       </c>
       <c r="I145">
-        <v>5.166475057601929</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -10143,7 +10143,7 @@
         <v>0</v>
       </c>
       <c r="I146">
-        <v>8.362907886505127</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -10172,7 +10172,7 @@
         <v>1</v>
       </c>
       <c r="I147">
-        <v>8.899328470230103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -10201,7 +10201,7 @@
         <v>1</v>
       </c>
       <c r="I148">
-        <v>24.35130262374878</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -10230,7 +10230,7 @@
         <v>1</v>
       </c>
       <c r="I149">
-        <v>5.358256340026855</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -10259,7 +10259,7 @@
         <v>1</v>
       </c>
       <c r="I150">
-        <v>5.230840921401978</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -10288,7 +10288,7 @@
         <v>0</v>
       </c>
       <c r="I151">
-        <v>5.335838317871094</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -10317,7 +10317,7 @@
         <v>0</v>
       </c>
       <c r="I152">
-        <v>42.54680705070496</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -10346,7 +10346,7 @@
         <v>1</v>
       </c>
       <c r="I153">
-        <v>8.78440260887146</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -10375,7 +10375,7 @@
         <v>0</v>
       </c>
       <c r="I154">
-        <v>24.17625546455383</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -10401,7 +10401,7 @@
         <v>0</v>
       </c>
       <c r="I155">
-        <v>31.37271738052368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -10430,7 +10430,7 @@
         <v>0</v>
       </c>
       <c r="I156">
-        <v>25.80688524246216</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -10459,7 +10459,7 @@
         <v>0</v>
       </c>
       <c r="I157">
-        <v>9.619369983673096</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -10488,7 +10488,7 @@
         <v>0</v>
       </c>
       <c r="I158">
-        <v>6.572101593017578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -10517,7 +10517,7 @@
         <v>0</v>
       </c>
       <c r="I159">
-        <v>22.03710007667542</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -10546,7 +10546,7 @@
         <v>0</v>
       </c>
       <c r="I160">
-        <v>7.156412839889526</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -10575,7 +10575,7 @@
         <v>0</v>
       </c>
       <c r="I161">
-        <v>6.739928245544434</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -10604,7 +10604,7 @@
         <v>1</v>
       </c>
       <c r="I162">
-        <v>16.72587609291077</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -10630,7 +10630,7 @@
         <v>0</v>
       </c>
       <c r="I163">
-        <v>26.34623885154724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -10659,7 +10659,7 @@
         <v>1</v>
       </c>
       <c r="I164">
-        <v>19.83455753326416</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -10688,7 +10688,7 @@
         <v>0</v>
       </c>
       <c r="I165">
-        <v>7.624080657958984</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -10717,7 +10717,7 @@
         <v>0</v>
       </c>
       <c r="I166">
-        <v>8.442744016647339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -10746,7 +10746,7 @@
         <v>0</v>
       </c>
       <c r="I167">
-        <v>39.27731561660767</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -10775,7 +10775,7 @@
         <v>1</v>
       </c>
       <c r="I168">
-        <v>6.865872859954834</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -10804,7 +10804,7 @@
         <v>1</v>
       </c>
       <c r="I169">
-        <v>6.948126316070557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -10833,7 +10833,7 @@
         <v>1</v>
       </c>
       <c r="I170">
-        <v>15.89315605163574</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -10862,7 +10862,7 @@
         <v>1</v>
       </c>
       <c r="I171">
-        <v>10.82041788101196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:9">
@@ -10891,7 +10891,7 @@
         <v>1</v>
       </c>
       <c r="I172">
-        <v>10.88729906082153</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:9">
@@ -10917,7 +10917,7 @@
         <v>0</v>
       </c>
       <c r="I173">
-        <v>30.10351204872131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:9">
@@ -10946,7 +10946,7 @@
         <v>0</v>
       </c>
       <c r="I174">
-        <v>6.563049554824829</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:9">
@@ -10975,7 +10975,7 @@
         <v>1</v>
       </c>
       <c r="I175">
-        <v>28.34595847129822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:9">
@@ -11004,7 +11004,7 @@
         <v>0</v>
       </c>
       <c r="I176">
-        <v>9.871282339096069</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:9">
@@ -11033,7 +11033,7 @@
         <v>0</v>
       </c>
       <c r="I177">
-        <v>25.91831636428833</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:9">
@@ -11062,7 +11062,7 @@
         <v>0</v>
       </c>
       <c r="I178">
-        <v>39.87558960914612</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:9">
@@ -11088,7 +11088,7 @@
         <v>0</v>
       </c>
       <c r="I179">
-        <v>30.19955539703369</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:9">
@@ -11117,7 +11117,7 @@
         <v>0</v>
       </c>
       <c r="I180">
-        <v>28.94222736358643</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:9">
@@ -11146,7 +11146,7 @@
         <v>0</v>
       </c>
       <c r="I181">
-        <v>36.82791924476624</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:9">
@@ -11175,7 +11175,7 @@
         <v>0</v>
       </c>
       <c r="I182">
-        <v>31.57015109062195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:9">
@@ -11204,7 +11204,7 @@
         <v>0</v>
       </c>
       <c r="I183">
-        <v>37.74453711509705</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:9">
@@ -11233,7 +11233,7 @@
         <v>0</v>
       </c>
       <c r="I184">
-        <v>28.29071807861328</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:9">
@@ -11262,7 +11262,7 @@
         <v>0</v>
       </c>
       <c r="I185">
-        <v>33.58607053756714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:9">
@@ -11291,7 +11291,7 @@
         <v>0</v>
       </c>
       <c r="I186">
-        <v>30.49300932884216</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:9">
@@ -11320,7 +11320,7 @@
         <v>1</v>
       </c>
       <c r="I187">
-        <v>6.285889863967896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:9">
@@ -11349,7 +11349,7 @@
         <v>0</v>
       </c>
       <c r="I188">
-        <v>25.55020546913147</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:9">
@@ -11375,7 +11375,7 @@
         <v>0</v>
       </c>
       <c r="I189">
-        <v>7.799176931381226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:9">
@@ -11404,7 +11404,7 @@
         <v>1</v>
       </c>
       <c r="I190">
-        <v>11.06124520301819</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:9">
@@ -11433,7 +11433,7 @@
         <v>0</v>
       </c>
       <c r="I191">
-        <v>21.05727219581604</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:9">
@@ -11462,7 +11462,7 @@
         <v>0</v>
       </c>
       <c r="I192">
-        <v>34.0770058631897</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:9">
@@ -11491,7 +11491,7 @@
         <v>0</v>
       </c>
       <c r="I193">
-        <v>33.60248684883118</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:9">
@@ -11520,7 +11520,7 @@
         <v>0</v>
       </c>
       <c r="I194">
-        <v>31.03739905357361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:9">
@@ -11549,7 +11549,7 @@
         <v>1</v>
       </c>
       <c r="I195">
-        <v>33.67480421066284</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:9">
@@ -11575,7 +11575,7 @@
         <v>0</v>
       </c>
       <c r="I196">
-        <v>26.65087652206421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:9">
@@ -11604,7 +11604,7 @@
         <v>1</v>
       </c>
       <c r="I197">
-        <v>32.91027522087097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -11633,7 +11633,7 @@
         <v>0</v>
       </c>
       <c r="I198">
-        <v>33.32345008850098</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -11662,7 +11662,7 @@
         <v>1</v>
       </c>
       <c r="I199">
-        <v>8.574735879898071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:9">
@@ -11691,7 +11691,7 @@
         <v>1</v>
       </c>
       <c r="I200">
-        <v>7.250335931777954</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -11720,7 +11720,7 @@
         <v>1</v>
       </c>
       <c r="I201">
-        <v>14.69690084457397</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
